--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -947,7 +947,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00126_19130805/oocihm.N_00126_19130805.3.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y77"/>
+  <dimension ref="A1:Y82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -609,16 +609,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L6: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 4.â€” An interesting</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]rentes</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]rentes</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L15: symbol-only separator/garbage line :: 1914.</t>
@@ -642,7 +646,7 @@
       <c r="R2" s="1" t="inlineStr"/>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L715: line starts with punctuation glued to text :: * SILK and CREPE KIMONAS. SEPARATE SKIRTS-In White</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Gleaner will be published on •</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -665,7 +669,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>774</t>
+          <t>564</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -688,12 +692,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -705,7 +709,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L9: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L9: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr">
@@ -719,7 +723,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pear in the Saturday issue)</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr"/>
@@ -763,24 +771,24 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L53: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L53: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L11: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr">
@@ -790,11 +798,15 @@
       </c>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L299: punctuation artifact: repeated periods :: TELEPHONE CO.. LTD</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ changes of advertisements ap- •</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr"/>
@@ -810,12 +822,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>101</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>68</t>
+          <t>50</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr"/>
@@ -838,12 +850,12 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L74: stray/suspicious non-ASCII glyph(s): U+7279 CJK UNIFIED IDEOGRAPH-7279 | isolated marker/symbol line :: 特</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L81: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 4.â€”An interesting</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -855,7 +867,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L13: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L13: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr">
@@ -865,11 +877,15 @@
       </c>
       <c r="Q5" s="1" t="inlineStr">
         <is>
-          <t>L418: punctuation artifact: repeated periods :: That experiment....</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L715: line starts with punctuation glued to text :: * SILK and CREPE KIMONAS. SEPARATE SKIRTS-In White</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr"/>
@@ -909,12 +925,12 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L75: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K6" s="1" t="inlineStr">
         <is>
-          <t>L126: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: letâ€� regiment.</t>
+          <t>L257: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Until further notice The •</t>
         </is>
       </c>
       <c r="L6" s="1" t="inlineStr"/>
@@ -932,7 +948,7 @@
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
         <is>
-          <t>L580: punctuation artifact: repeated periods :: ......New Majestic</t>
+          <t>L299: punctuation artifact: repeated periods :: TELEPHONE CO.. LTD</t>
         </is>
       </c>
       <c r="R6" s="1" t="inlineStr"/>
@@ -972,12 +988,12 @@
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L78: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K7" s="1" t="inlineStr">
         <is>
-          <t>L169: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY, CHIFFONIER â€” Ma-</t>
+          <t>L259: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Gleaner will be published on •</t>
         </is>
       </c>
       <c r="L7" s="1" t="inlineStr"/>
@@ -995,7 +1011,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L582: punctuation artifact: repeated periods :: .. Keystone Comedy</t>
+          <t>L418: punctuation artifact: repeated periods :: That experiment....</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -1035,12 +1051,12 @@
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K8" s="1" t="inlineStr">
         <is>
-          <t>L177: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY, PARLOR SUITEâ€”</t>
+          <t>L260: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: res. • Saturdays at noon.•</t>
         </is>
       </c>
       <c r="L8" s="1" t="inlineStr"/>
@@ -1058,7 +1074,7 @@
       <c r="P8" s="1" t="inlineStr"/>
       <c r="Q8" s="1" t="inlineStr">
         <is>
-          <t>L584: punctuation artifact: repeated periods :: ............3 Reels</t>
+          <t>L580: punctuation artifact: repeated periods :: ......New Majestic</t>
         </is>
       </c>
       <c r="R8" s="1" t="inlineStr"/>
@@ -1098,12 +1114,12 @@
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L138: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€” AT-</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K9" s="1" t="inlineStr">
         <is>
-          <t>L193: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 1 ONLY DINNER SETâ€”A very</t>
+          <t>L262: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Advertisers in order to have •</t>
         </is>
       </c>
       <c r="L9" s="1" t="inlineStr"/>
@@ -1121,7 +1137,7 @@
       <c r="P9" s="1" t="inlineStr"/>
       <c r="Q9" s="1" t="inlineStr">
         <is>
-          <t>L586: punctuation artifact: repeated periods :: DEAD MAN'S SHOES ...........</t>
+          <t>L582: punctuation artifact: repeated periods :: .. Keystone Comedy</t>
         </is>
       </c>
       <c r="R9" s="1" t="inlineStr"/>
@@ -1141,12 +1157,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>16</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1155,18 +1171,18 @@
       <c r="G10" s="1" t="inlineStr"/>
       <c r="H10" s="1" t="inlineStr">
         <is>
-          <t>L729: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): WAISTSIn (odd internal casing) :: LADIESâ€™WAISTSIn all the various kinds wanted by those who</t>
+          <t>L729: suspicious token(s): LADIES’WAISTSIn (odd internal casing) :: LADIES’WAISTSIn all the various kinds wanted by those who</t>
         </is>
       </c>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L141: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ONLY, NLY, DRESSERSâ€”Surface</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K10" s="1" t="inlineStr">
         <is>
-          <t>L214: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: what the neighbors say," she doesnâ€™t</t>
+          <t>L279: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: CHATEAU €</t>
         </is>
       </c>
       <c r="L10" s="1" t="inlineStr"/>
@@ -1184,7 +1200,7 @@
       <c r="P10" s="1" t="inlineStr"/>
       <c r="Q10" s="1" t="inlineStr">
         <is>
-          <t>L588: punctuation artifact: repeated periods :: HIS SACRIFICE ..............</t>
+          <t>L584: punctuation artifact: repeated periods :: ............3 Reels</t>
         </is>
       </c>
       <c r="R10" s="1" t="inlineStr"/>
@@ -1209,7 +1225,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1224,19 +1240,19 @@
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L156: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ONLY, CHIFFONIERâ€”Ma-</t>
+          <t>L143: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN :: 16×20, 3 large drawers; the.</t>
         </is>
       </c>
       <c r="K11" s="1" t="inlineStr">
         <is>
-          <t>L257: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Until further notice The â€¢</t>
+          <t>L282: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET | punctuation artifact: hyphen/bullet debris :: ♦ changes of advertisements ap- •</t>
         </is>
       </c>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L60: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L60: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1247,7 +1263,7 @@
       <c r="P11" s="1" t="inlineStr"/>
       <c r="Q11" s="1" t="inlineStr">
         <is>
-          <t>L590: punctuation artifact: repeated periods :: SIDETRACKED BY SISTER ......</t>
+          <t>L586: punctuation artifact: repeated periods :: DEAD MAN'S SHOES ...........</t>
         </is>
       </c>
       <c r="R11" s="1" t="inlineStr"/>
@@ -1267,12 +1283,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>76</t>
+          <t>81</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>21</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1283,12 +1299,12 @@
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L166: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: SUITE â€”</t>
+          <t>L160: stray/suspicious non-ASCII glyph(s): U+00D7 MULTIPLICATION SIGN :: mirror 16×18, 4 large drawers</t>
         </is>
       </c>
       <c r="K12" s="1" t="inlineStr">
         <is>
-          <t>L259: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Gleaner will be published on â€¢</t>
+          <t>L283: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • pear in the Saturday issue)</t>
         </is>
       </c>
       <c r="L12" s="1" t="inlineStr"/>
@@ -1306,7 +1322,7 @@
       <c r="P12" s="1" t="inlineStr"/>
       <c r="Q12" s="1" t="inlineStr">
         <is>
-          <t>L592: punctuation artifact: repeated periods :: TOPLITSKY &amp; CO..............</t>
+          <t>L588: punctuation artifact: repeated periods :: HIS SACRIFICE ..............</t>
         </is>
       </c>
       <c r="R12" s="1" t="inlineStr"/>
@@ -1331,7 +1347,7 @@
       </c>
       <c r="C13" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="D13" s="1" t="inlineStr"/>
@@ -1342,12 +1358,12 @@
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L176: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="K13" s="1" t="inlineStr">
         <is>
-          <t>L260: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: res. â€¢ Saturdays at noon.â€¢</t>
+          <t>L284: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ should have their copy at The •</t>
         </is>
       </c>
       <c r="L13" s="1" t="inlineStr"/>
@@ -1363,7 +1379,11 @@
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
-      <c r="Q13" s="1" t="inlineStr"/>
+      <c r="Q13" s="1" t="inlineStr">
+        <is>
+          <t>L590: punctuation artifact: repeated periods :: SIDETRACKED BY SISTER ......</t>
+        </is>
+      </c>
       <c r="R13" s="1" t="inlineStr"/>
       <c r="S13" s="1" t="inlineStr"/>
       <c r="T13" s="1" t="inlineStr"/>
@@ -1386,7 +1406,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1397,12 +1417,12 @@
       <c r="I14" s="1" t="inlineStr"/>
       <c r="J14" s="1" t="inlineStr">
         <is>
-          <t>L256: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Efforts io Settle Vexed Question â€” Whole Trouble</t>
+          <t>L244: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="K14" s="1" t="inlineStr">
         <is>
-          <t>L262: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Advertisers in order to have â€¢</t>
+          <t>L285: stray/suspicious non-ASCII glyph(s): U+2666 BLACK DIAMOND SUIT, U+2022 BULLET :: ♦ Gleaner office not later than •</t>
         </is>
       </c>
       <c r="L14" s="1" t="inlineStr"/>
@@ -1418,7 +1438,11 @@
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
-      <c r="Q14" s="1" t="inlineStr"/>
+      <c r="Q14" s="1" t="inlineStr">
+        <is>
+          <t>L592: punctuation artifact: repeated periods :: TOPLITSKY &amp; CO..............</t>
+        </is>
+      </c>
       <c r="R14" s="1" t="inlineStr"/>
       <c r="S14" s="1" t="inlineStr"/>
       <c r="T14" s="1" t="inlineStr"/>
@@ -1452,12 +1476,12 @@
       <c r="I15" s="1" t="inlineStr"/>
       <c r="J15" s="1" t="inlineStr">
         <is>
-          <t>L276: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has paid attention â€”" has a lot to learn</t>
+          <t>L700: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
         </is>
       </c>
       <c r="K15" s="1" t="inlineStr">
         <is>
-          <t>L272: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 32â€”Monahan, Mrs. T. V.,</t>
+          <t>L286: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | punctuation artifact: hyphen/bullet debris | line starts with punctuation glued to text :: • 4.30 o'clock on Friday after-•</t>
         </is>
       </c>
       <c r="L15" s="1" t="inlineStr"/>
@@ -1505,14 +1529,10 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr"/>
       <c r="I16" s="1" t="inlineStr"/>
-      <c r="J16" s="1" t="inlineStr">
-        <is>
-          <t>L348: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 4.â€”</t>
-        </is>
-      </c>
+      <c r="J16" s="1" t="inlineStr"/>
       <c r="K16" s="1" t="inlineStr">
         <is>
-          <t>L275: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 126-21â€”Kitchen, Mrs. S., res.</t>
+          <t>L287: stray/suspicious non-ASCII glyph(s): U+2022 BULLET :: &amp; noon •</t>
         </is>
       </c>
       <c r="L16" s="1" t="inlineStr"/>
@@ -1560,14 +1580,10 @@
       <c r="G17" s="1" t="inlineStr"/>
       <c r="H17" s="1" t="inlineStr"/>
       <c r="I17" s="1" t="inlineStr"/>
-      <c r="J17" s="1" t="inlineStr">
-        <is>
-          <t>L396: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 5 â€” The Daily Tele-across the ocean would be doubly so.</t>
-        </is>
-      </c>
+      <c r="J17" s="1" t="inlineStr"/>
       <c r="K17" s="1" t="inlineStr">
         <is>
-          <t>L279: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: CHATEAU â‚¬</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L17" s="1" t="inlineStr"/>
@@ -1603,26 +1619,18 @@
       <c r="G18" s="1" t="inlineStr"/>
       <c r="H18" s="1" t="inlineStr"/>
       <c r="I18" s="1" t="inlineStr"/>
-      <c r="J18" s="1" t="inlineStr">
-        <is>
-          <t>L403: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Aug. 4.â€” Seven people,</t>
-        </is>
-      </c>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L280: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: A BRANDâ€”</t>
-        </is>
-      </c>
+      <c r="J18" s="1" t="inlineStr"/>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: æ°”</t>
+          <t>L67: stray/suspicious non-ASCII glyph(s): U+6C14 CJK UNIFIED IDEOGRAPH-6C14 | isolated marker/symbol line :: 气</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L734: isolated marker/symbol line :: 1</t>
+          <t>L663: symbol-only separator/garbage line :: 7.30—10.30</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1646,16 +1654,8 @@
       <c r="G19" s="1" t="inlineStr"/>
       <c r="H19" s="1" t="inlineStr"/>
       <c r="I19" s="1" t="inlineStr"/>
-      <c r="J19" s="1" t="inlineStr">
-        <is>
-          <t>L652: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: WEDNESDAY â€” THE</t>
-        </is>
-      </c>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L282: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ changes of advertisements ap- â€¢</t>
-        </is>
-      </c>
+      <c r="J19" s="1" t="inlineStr"/>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
@@ -1665,7 +1665,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L734: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1689,16 +1689,8 @@
       <c r="G20" s="1" t="inlineStr"/>
       <c r="H20" s="1" t="inlineStr"/>
       <c r="I20" s="1" t="inlineStr"/>
-      <c r="J20" s="1" t="inlineStr">
-        <is>
-          <t>L656: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.30 â€” 10.30</t>
-        </is>
-      </c>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L283: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ pear in the Saturday issue)</t>
-        </is>
-      </c>
+      <c r="J20" s="1" t="inlineStr"/>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
@@ -1708,7 +1700,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L736: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1732,16 +1724,8 @@
       <c r="G21" s="1" t="inlineStr"/>
       <c r="H21" s="1" t="inlineStr"/>
       <c r="I21" s="1" t="inlineStr"/>
-      <c r="J21" s="1" t="inlineStr">
-        <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
-        </is>
-      </c>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L284: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ should have their copy at The â€¢</t>
-        </is>
-      </c>
+      <c r="J21" s="1" t="inlineStr"/>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
@@ -1751,7 +1735,7 @@
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L761: isolated marker/symbol line :: (A</t>
+          <t>L757: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1775,16 +1759,8 @@
       <c r="G22" s="1" t="inlineStr"/>
       <c r="H22" s="1" t="inlineStr"/>
       <c r="I22" s="1" t="inlineStr"/>
-      <c r="J22" s="1" t="inlineStr">
-        <is>
-          <t>L718: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LOTH COSTUMES â€” Just a few to clear at the wonderfully low</t>
-        </is>
-      </c>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L285: stray/suspicious non-ASCII glyph(s): U+2122 TRADE MARK SIGN, U+00A6 BROKEN BAR, U+20AC EURO SIGN, U+00A2 CENT SIGN :: â™¦ Gleaner office not later than â€¢</t>
-        </is>
-      </c>
+      <c r="J22" s="1" t="inlineStr"/>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
@@ -1792,7 +1768,11 @@
           <t>L71: isolated marker/symbol line :: 2</t>
         </is>
       </c>
-      <c r="O22" s="1" t="inlineStr"/>
+      <c r="O22" s="1" t="inlineStr">
+        <is>
+          <t>L761: isolated marker/symbol line :: (A</t>
+        </is>
+      </c>
       <c r="P22" s="1" t="inlineStr"/>
       <c r="Q22" s="1" t="inlineStr"/>
       <c r="R22" s="1" t="inlineStr"/>
@@ -1814,16 +1794,8 @@
       <c r="G23" s="1" t="inlineStr"/>
       <c r="H23" s="1" t="inlineStr"/>
       <c r="I23" s="1" t="inlineStr"/>
-      <c r="J23" s="1" t="inlineStr">
-        <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: LADIESâ€™LONG COATS â€” Very Stylish, in Silk, Lace, Poplin,</t>
-        </is>
-      </c>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L286: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 4.30 o'clock on Friday after-â€¢</t>
-        </is>
-      </c>
+      <c r="J23" s="1" t="inlineStr"/>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
@@ -1853,16 +1825,8 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr"/>
       <c r="I24" s="1" t="inlineStr"/>
-      <c r="J24" s="1" t="inlineStr">
-        <is>
-          <t>L722: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRETTY DRESSES â€” In Silk, White and Colored Serge, Linen</t>
-        </is>
-      </c>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L287: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: &amp; noon â€¢</t>
-        </is>
-      </c>
+      <c r="J24" s="1" t="inlineStr"/>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
@@ -1892,21 +1856,13 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr"/>
       <c r="I25" s="1" t="inlineStr"/>
-      <c r="J25" s="1" t="inlineStr">
-        <is>
-          <t>L729: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): WAISTSIn (odd internal casing) :: LADIESâ€™WAISTSIn all the various kinds wanted by those who</t>
-        </is>
-      </c>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L304: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Efforts to Settle Vexed Questionâ€” Whole Trouble</t>
-        </is>
-      </c>
+      <c r="J25" s="1" t="inlineStr"/>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L75: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L74: stray/suspicious non-ASCII glyph(s): U+7279 CJK UNIFIED IDEOGRAPH-7279 | isolated marker/symbol line :: 特</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr"/>
@@ -1932,16 +1888,12 @@
       <c r="H26" s="1" t="inlineStr"/>
       <c r="I26" s="1" t="inlineStr"/>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L310: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Quebec, Aug. 4.â€”Seven people,</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 2</t>
+          <t>L75: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr"/>
@@ -1967,16 +1919,12 @@
       <c r="H27" s="1" t="inlineStr"/>
       <c r="I27" s="1" t="inlineStr"/>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L337: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Ottawa, Aug. 5â€”The Daily Tele-</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L77: isolated marker/symbol line :: 4</t>
+          <t>L76: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr"/>
@@ -2002,16 +1950,12 @@
       <c r="H28" s="1" t="inlineStr"/>
       <c r="I28" s="1" t="inlineStr"/>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L419: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: has paid attentionâ€” has a lot to learn</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L78: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L77: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr"/>
@@ -2037,16 +1981,12 @@
       <c r="H29" s="1" t="inlineStr"/>
       <c r="I29" s="1" t="inlineStr"/>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L453: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: posalâ€”discouraged itâ€”sneered at it.</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L79: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L78: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr"/>
@@ -2072,16 +2012,12 @@
       <c r="H30" s="1" t="inlineStr"/>
       <c r="I30" s="1" t="inlineStr"/>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L463: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Sir Wilfrid Laurierâ€™s Government</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L80: isolated marker/symbol line :: 2</t>
+          <t>L79: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr"/>
@@ -2107,16 +2043,12 @@
       <c r="H31" s="1" t="inlineStr"/>
       <c r="I31" s="1" t="inlineStr"/>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L500: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Rev. Dr, W. H. Smithâ€™s Views</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L81: isolated marker/symbol line :: X</t>
+          <t>L80: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr"/>
@@ -2142,16 +2074,12 @@
       <c r="H32" s="1" t="inlineStr"/>
       <c r="I32" s="1" t="inlineStr"/>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L558: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+02DC SMALL TILDE :: -_ /â€˜yers for those whom</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L82: isolated marker/symbol line :: :</t>
+          <t>L81: isolated marker/symbol line :: X</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr"/>
@@ -2177,16 +2105,12 @@
       <c r="H33" s="1" t="inlineStr"/>
       <c r="I33" s="1" t="inlineStr"/>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L654: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: LADIES' LONG COATSâ€” Very Stylish, in Silk, Lace, Poplin,</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L83: isolated marker/symbol line :: ,</t>
+          <t>L82: isolated marker/symbol line :: :</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr"/>
@@ -2212,16 +2136,12 @@
       <c r="H34" s="1" t="inlineStr"/>
       <c r="I34" s="1" t="inlineStr"/>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L663: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 7.30â€”10.30</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L84: isolated marker/symbol line :: 4</t>
+          <t>L83: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O34" s="1" t="inlineStr"/>
@@ -2247,16 +2167,12 @@
       <c r="H35" s="1" t="inlineStr"/>
       <c r="I35" s="1" t="inlineStr"/>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L676: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: PRETTY DRESSES â€” In Silk, White and Colored Serge, Linen</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 3</t>
+          <t>L84: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O35" s="1" t="inlineStr"/>
@@ -2282,16 +2198,12 @@
       <c r="H36" s="1" t="inlineStr"/>
       <c r="I36" s="1" t="inlineStr"/>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L736: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 4</t>
+          <t>L86: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O36" s="1" t="inlineStr"/>
@@ -2317,16 +2229,12 @@
       <c r="H37" s="1" t="inlineStr"/>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L757: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: v</t>
+          <t>L87: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O37" s="1" t="inlineStr"/>
@@ -2357,7 +2265,7 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: 2</t>
+          <t>L88: isolated marker/symbol line :: v</t>
         </is>
       </c>
       <c r="O38" s="1" t="inlineStr"/>
@@ -2388,7 +2296,7 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L90: isolated marker/symbol line :: .</t>
+          <t>L89: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O39" s="1" t="inlineStr"/>
@@ -2419,7 +2327,7 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L92: isolated marker/symbol line :: 2</t>
+          <t>L90: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O40" s="1" t="inlineStr"/>
@@ -2450,7 +2358,7 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L93: isolated marker/symbol line :: 7</t>
+          <t>L91: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O41" s="1" t="inlineStr"/>
@@ -2481,7 +2389,7 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L94: isolated marker/symbol line :: .</t>
+          <t>L92: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O42" s="1" t="inlineStr"/>
@@ -2512,7 +2420,7 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 2</t>
+          <t>L93: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O43" s="1" t="inlineStr"/>
@@ -2543,7 +2451,7 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L96: isolated marker/symbol line :: 7</t>
+          <t>L94: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O44" s="1" t="inlineStr"/>
@@ -2574,7 +2482,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L97: isolated marker/symbol line :: ,</t>
+          <t>L95: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2605,7 +2513,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L98: isolated marker/symbol line :: 4</t>
+          <t>L96: isolated marker/symbol line :: 7</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2636,7 +2544,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L99: isolated marker/symbol line :: 2</t>
+          <t>L97: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2667,7 +2575,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L100: isolated marker/symbol line :: V</t>
+          <t>L98: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2698,7 +2606,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L101: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L99: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2729,7 +2637,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L102: isolated marker/symbol line :: 5</t>
+          <t>L100: isolated marker/symbol line :: V</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2760,7 +2668,7 @@
       <c r="M51" s="1" t="inlineStr"/>
       <c r="N51" s="1" t="inlineStr">
         <is>
-          <t>L103: isolated marker/symbol line :: 2</t>
+          <t>L101: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O51" s="1" t="inlineStr"/>
@@ -2791,7 +2699,7 @@
       <c r="M52" s="1" t="inlineStr"/>
       <c r="N52" s="1" t="inlineStr">
         <is>
-          <t>L140: isolated marker/symbol line :: 6</t>
+          <t>L102: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O52" s="1" t="inlineStr"/>
@@ -2822,7 +2730,7 @@
       <c r="M53" s="1" t="inlineStr"/>
       <c r="N53" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: 97</t>
+          <t>L103: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O53" s="1" t="inlineStr"/>
@@ -2853,7 +2761,7 @@
       <c r="M54" s="1" t="inlineStr"/>
       <c r="N54" s="1" t="inlineStr">
         <is>
-          <t>L154: symbol-only separator/garbage line :: $5 85</t>
+          <t>L140: isolated marker/symbol line :: 6</t>
         </is>
       </c>
       <c r="O54" s="1" t="inlineStr"/>
@@ -2884,7 +2792,7 @@
       <c r="M55" s="1" t="inlineStr"/>
       <c r="N55" s="1" t="inlineStr">
         <is>
-          <t>L155: isolated marker/symbol line :: 1</t>
+          <t>L150: isolated marker/symbol line :: 97</t>
         </is>
       </c>
       <c r="O55" s="1" t="inlineStr"/>
@@ -2915,7 +2823,7 @@
       <c r="M56" s="1" t="inlineStr"/>
       <c r="N56" s="1" t="inlineStr">
         <is>
-          <t>L164: isolated marker/symbol line :: 1</t>
+          <t>L154: symbol-only separator/garbage line :: $5 85</t>
         </is>
       </c>
       <c r="O56" s="1" t="inlineStr"/>
@@ -2946,7 +2854,7 @@
       <c r="M57" s="1" t="inlineStr"/>
       <c r="N57" s="1" t="inlineStr">
         <is>
-          <t>L183: isolated marker/symbol line :: 3</t>
+          <t>L155: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O57" s="1" t="inlineStr"/>
@@ -2977,7 +2885,7 @@
       <c r="M58" s="1" t="inlineStr"/>
       <c r="N58" s="1" t="inlineStr">
         <is>
-          <t>L188: isolated marker/symbol line :: 4.</t>
+          <t>L164: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O58" s="1" t="inlineStr"/>
@@ -3008,7 +2916,7 @@
       <c r="M59" s="1" t="inlineStr"/>
       <c r="N59" s="1" t="inlineStr">
         <is>
-          <t>L196: isolated marker/symbol line :: 2</t>
+          <t>L176: stray/suspicious non-ASCII glyph(s): U+2212 MINUS SIGN | isolated marker/symbol line :: −</t>
         </is>
       </c>
       <c r="O59" s="1" t="inlineStr"/>
@@ -3039,7 +2947,7 @@
       <c r="M60" s="1" t="inlineStr"/>
       <c r="N60" s="1" t="inlineStr">
         <is>
-          <t>L233: isolated marker/symbol line :: a</t>
+          <t>L183: isolated marker/symbol line :: 3</t>
         </is>
       </c>
       <c r="O60" s="1" t="inlineStr"/>
@@ -3070,7 +2978,7 @@
       <c r="M61" s="1" t="inlineStr"/>
       <c r="N61" s="1" t="inlineStr">
         <is>
-          <t>L242: isolated marker/symbol line :: 1</t>
+          <t>L188: isolated marker/symbol line :: 4.</t>
         </is>
       </c>
       <c r="O61" s="1" t="inlineStr"/>
@@ -3101,7 +3009,7 @@
       <c r="M62" s="1" t="inlineStr"/>
       <c r="N62" s="1" t="inlineStr">
         <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+00A6 BROKEN BAR, U+FFFD REPLACEMENT CHARACTER | isolated marker/symbol line :: ç¦�</t>
+          <t>L196: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O62" s="1" t="inlineStr"/>
@@ -3132,7 +3040,7 @@
       <c r="M63" s="1" t="inlineStr"/>
       <c r="N63" s="1" t="inlineStr">
         <is>
-          <t>L447: isolated marker/symbol line :: 0</t>
+          <t>L233: isolated marker/symbol line :: a</t>
         </is>
       </c>
       <c r="O63" s="1" t="inlineStr"/>
@@ -3163,7 +3071,7 @@
       <c r="M64" s="1" t="inlineStr"/>
       <c r="N64" s="1" t="inlineStr">
         <is>
-          <t>L456: isolated marker/symbol line :: s.,</t>
+          <t>L242: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O64" s="1" t="inlineStr"/>
@@ -3194,7 +3102,7 @@
       <c r="M65" s="1" t="inlineStr"/>
       <c r="N65" s="1" t="inlineStr">
         <is>
-          <t>L458: isolated marker/symbol line :: 317</t>
+          <t>L244: stray/suspicious non-ASCII glyph(s): U+798F CJK UNIFIED IDEOGRAPH-798F | isolated marker/symbol line :: 福</t>
         </is>
       </c>
       <c r="O65" s="1" t="inlineStr"/>
@@ -3225,7 +3133,7 @@
       <c r="M66" s="1" t="inlineStr"/>
       <c r="N66" s="1" t="inlineStr">
         <is>
-          <t>L465: isolated marker/symbol line :: 5</t>
+          <t>L348: isolated marker/symbol line :: 4.—</t>
         </is>
       </c>
       <c r="O66" s="1" t="inlineStr"/>
@@ -3256,7 +3164,7 @@
       <c r="M67" s="1" t="inlineStr"/>
       <c r="N67" s="1" t="inlineStr">
         <is>
-          <t>L501: isolated marker/symbol line :: 9</t>
+          <t>L447: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O67" s="1" t="inlineStr"/>
@@ -3287,7 +3195,7 @@
       <c r="M68" s="1" t="inlineStr"/>
       <c r="N68" s="1" t="inlineStr">
         <is>
-          <t>L506: isolated marker/symbol line :: 1</t>
+          <t>L456: isolated marker/symbol line :: s.,</t>
         </is>
       </c>
       <c r="O68" s="1" t="inlineStr"/>
@@ -3318,7 +3226,7 @@
       <c r="M69" s="1" t="inlineStr"/>
       <c r="N69" s="1" t="inlineStr">
         <is>
-          <t>L509: isolated marker/symbol line :: &amp;</t>
+          <t>L458: isolated marker/symbol line :: 317</t>
         </is>
       </c>
       <c r="O69" s="1" t="inlineStr"/>
@@ -3349,7 +3257,7 @@
       <c r="M70" s="1" t="inlineStr"/>
       <c r="N70" s="1" t="inlineStr">
         <is>
-          <t>L511: isolated marker/symbol line :: 4</t>
+          <t>L465: isolated marker/symbol line :: 5</t>
         </is>
       </c>
       <c r="O70" s="1" t="inlineStr"/>
@@ -3380,7 +3288,7 @@
       <c r="M71" s="1" t="inlineStr"/>
       <c r="N71" s="1" t="inlineStr">
         <is>
-          <t>L644: isolated marker/symbol line :: .</t>
+          <t>L501: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="O71" s="1" t="inlineStr"/>
@@ -3411,7 +3319,7 @@
       <c r="M72" s="1" t="inlineStr"/>
       <c r="N72" s="1" t="inlineStr">
         <is>
-          <t>L651: isolated marker/symbol line :: &amp;</t>
+          <t>L506: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O72" s="1" t="inlineStr"/>
@@ -3442,7 +3350,7 @@
       <c r="M73" s="1" t="inlineStr"/>
       <c r="N73" s="1" t="inlineStr">
         <is>
-          <t>L658: isolated marker/symbol line :: .</t>
+          <t>L509: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O73" s="1" t="inlineStr"/>
@@ -3473,7 +3381,7 @@
       <c r="M74" s="1" t="inlineStr"/>
       <c r="N74" s="1" t="inlineStr">
         <is>
-          <t>L697: isolated marker/symbol line :: n</t>
+          <t>L511: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O74" s="1" t="inlineStr"/>
@@ -3504,7 +3412,7 @@
       <c r="M75" s="1" t="inlineStr"/>
       <c r="N75" s="1" t="inlineStr">
         <is>
-          <t>L700: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+20AC EURO SIGN | isolated marker/symbol line :: ä¸€</t>
+          <t>L644: isolated marker/symbol line :: .</t>
         </is>
       </c>
       <c r="O75" s="1" t="inlineStr"/>
@@ -3535,7 +3443,7 @@
       <c r="M76" s="1" t="inlineStr"/>
       <c r="N76" s="1" t="inlineStr">
         <is>
-          <t>L703: isolated marker/symbol line :: f</t>
+          <t>L651: isolated marker/symbol line :: &amp;</t>
         </is>
       </c>
       <c r="O76" s="1" t="inlineStr"/>
@@ -3566,7 +3474,7 @@
       <c r="M77" s="1" t="inlineStr"/>
       <c r="N77" s="1" t="inlineStr">
         <is>
-          <t>L704: isolated marker/symbol line :: 1</t>
+          <t>L656: symbol-only separator/garbage line :: 7.30 — 10.30</t>
         </is>
       </c>
       <c r="O77" s="1" t="inlineStr"/>
@@ -3581,6 +3489,161 @@
       <c r="X77" s="1" t="inlineStr"/>
       <c r="Y77" s="1" t="inlineStr"/>
     </row>
+    <row r="78">
+      <c r="A78" s="1" t="inlineStr"/>
+      <c r="B78" s="1" t="inlineStr"/>
+      <c r="C78" s="1" t="inlineStr"/>
+      <c r="D78" s="1" t="inlineStr"/>
+      <c r="E78" s="1" t="inlineStr"/>
+      <c r="F78" s="1" t="inlineStr"/>
+      <c r="G78" s="1" t="inlineStr"/>
+      <c r="H78" s="1" t="inlineStr"/>
+      <c r="I78" s="1" t="inlineStr"/>
+      <c r="J78" s="1" t="inlineStr"/>
+      <c r="K78" s="1" t="inlineStr"/>
+      <c r="L78" s="1" t="inlineStr"/>
+      <c r="M78" s="1" t="inlineStr"/>
+      <c r="N78" s="1" t="inlineStr">
+        <is>
+          <t>L658: isolated marker/symbol line :: .</t>
+        </is>
+      </c>
+      <c r="O78" s="1" t="inlineStr"/>
+      <c r="P78" s="1" t="inlineStr"/>
+      <c r="Q78" s="1" t="inlineStr"/>
+      <c r="R78" s="1" t="inlineStr"/>
+      <c r="S78" s="1" t="inlineStr"/>
+      <c r="T78" s="1" t="inlineStr"/>
+      <c r="U78" s="1" t="inlineStr"/>
+      <c r="V78" s="1" t="inlineStr"/>
+      <c r="W78" s="1" t="inlineStr"/>
+      <c r="X78" s="1" t="inlineStr"/>
+      <c r="Y78" s="1" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="inlineStr"/>
+      <c r="B79" s="1" t="inlineStr"/>
+      <c r="C79" s="1" t="inlineStr"/>
+      <c r="D79" s="1" t="inlineStr"/>
+      <c r="E79" s="1" t="inlineStr"/>
+      <c r="F79" s="1" t="inlineStr"/>
+      <c r="G79" s="1" t="inlineStr"/>
+      <c r="H79" s="1" t="inlineStr"/>
+      <c r="I79" s="1" t="inlineStr"/>
+      <c r="J79" s="1" t="inlineStr"/>
+      <c r="K79" s="1" t="inlineStr"/>
+      <c r="L79" s="1" t="inlineStr"/>
+      <c r="M79" s="1" t="inlineStr"/>
+      <c r="N79" s="1" t="inlineStr">
+        <is>
+          <t>L697: isolated marker/symbol line :: n</t>
+        </is>
+      </c>
+      <c r="O79" s="1" t="inlineStr"/>
+      <c r="P79" s="1" t="inlineStr"/>
+      <c r="Q79" s="1" t="inlineStr"/>
+      <c r="R79" s="1" t="inlineStr"/>
+      <c r="S79" s="1" t="inlineStr"/>
+      <c r="T79" s="1" t="inlineStr"/>
+      <c r="U79" s="1" t="inlineStr"/>
+      <c r="V79" s="1" t="inlineStr"/>
+      <c r="W79" s="1" t="inlineStr"/>
+      <c r="X79" s="1" t="inlineStr"/>
+      <c r="Y79" s="1" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="inlineStr"/>
+      <c r="B80" s="1" t="inlineStr"/>
+      <c r="C80" s="1" t="inlineStr"/>
+      <c r="D80" s="1" t="inlineStr"/>
+      <c r="E80" s="1" t="inlineStr"/>
+      <c r="F80" s="1" t="inlineStr"/>
+      <c r="G80" s="1" t="inlineStr"/>
+      <c r="H80" s="1" t="inlineStr"/>
+      <c r="I80" s="1" t="inlineStr"/>
+      <c r="J80" s="1" t="inlineStr"/>
+      <c r="K80" s="1" t="inlineStr"/>
+      <c r="L80" s="1" t="inlineStr"/>
+      <c r="M80" s="1" t="inlineStr"/>
+      <c r="N80" s="1" t="inlineStr">
+        <is>
+          <t>L700: stray/suspicious non-ASCII glyph(s): U+4E00 CJK UNIFIED IDEOGRAPH-4E00 | isolated marker/symbol line :: 一</t>
+        </is>
+      </c>
+      <c r="O80" s="1" t="inlineStr"/>
+      <c r="P80" s="1" t="inlineStr"/>
+      <c r="Q80" s="1" t="inlineStr"/>
+      <c r="R80" s="1" t="inlineStr"/>
+      <c r="S80" s="1" t="inlineStr"/>
+      <c r="T80" s="1" t="inlineStr"/>
+      <c r="U80" s="1" t="inlineStr"/>
+      <c r="V80" s="1" t="inlineStr"/>
+      <c r="W80" s="1" t="inlineStr"/>
+      <c r="X80" s="1" t="inlineStr"/>
+      <c r="Y80" s="1" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="inlineStr"/>
+      <c r="B81" s="1" t="inlineStr"/>
+      <c r="C81" s="1" t="inlineStr"/>
+      <c r="D81" s="1" t="inlineStr"/>
+      <c r="E81" s="1" t="inlineStr"/>
+      <c r="F81" s="1" t="inlineStr"/>
+      <c r="G81" s="1" t="inlineStr"/>
+      <c r="H81" s="1" t="inlineStr"/>
+      <c r="I81" s="1" t="inlineStr"/>
+      <c r="J81" s="1" t="inlineStr"/>
+      <c r="K81" s="1" t="inlineStr"/>
+      <c r="L81" s="1" t="inlineStr"/>
+      <c r="M81" s="1" t="inlineStr"/>
+      <c r="N81" s="1" t="inlineStr">
+        <is>
+          <t>L703: isolated marker/symbol line :: f</t>
+        </is>
+      </c>
+      <c r="O81" s="1" t="inlineStr"/>
+      <c r="P81" s="1" t="inlineStr"/>
+      <c r="Q81" s="1" t="inlineStr"/>
+      <c r="R81" s="1" t="inlineStr"/>
+      <c r="S81" s="1" t="inlineStr"/>
+      <c r="T81" s="1" t="inlineStr"/>
+      <c r="U81" s="1" t="inlineStr"/>
+      <c r="V81" s="1" t="inlineStr"/>
+      <c r="W81" s="1" t="inlineStr"/>
+      <c r="X81" s="1" t="inlineStr"/>
+      <c r="Y81" s="1" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="inlineStr"/>
+      <c r="B82" s="1" t="inlineStr"/>
+      <c r="C82" s="1" t="inlineStr"/>
+      <c r="D82" s="1" t="inlineStr"/>
+      <c r="E82" s="1" t="inlineStr"/>
+      <c r="F82" s="1" t="inlineStr"/>
+      <c r="G82" s="1" t="inlineStr"/>
+      <c r="H82" s="1" t="inlineStr"/>
+      <c r="I82" s="1" t="inlineStr"/>
+      <c r="J82" s="1" t="inlineStr"/>
+      <c r="K82" s="1" t="inlineStr"/>
+      <c r="L82" s="1" t="inlineStr"/>
+      <c r="M82" s="1" t="inlineStr"/>
+      <c r="N82" s="1" t="inlineStr">
+        <is>
+          <t>L704: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
+      <c r="O82" s="1" t="inlineStr"/>
+      <c r="P82" s="1" t="inlineStr"/>
+      <c r="Q82" s="1" t="inlineStr"/>
+      <c r="R82" s="1" t="inlineStr"/>
+      <c r="S82" s="1" t="inlineStr"/>
+      <c r="T82" s="1" t="inlineStr"/>
+      <c r="U82" s="1" t="inlineStr"/>
+      <c r="V82" s="1" t="inlineStr"/>
+      <c r="W82" s="1" t="inlineStr"/>
+      <c r="X82" s="1" t="inlineStr"/>
+      <c r="Y82" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
